--- a/05_Figures/F06_prediction/modules/T3/d_fcsa_I/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/modules/T3/d_fcsa_I/spls/c_data/results.xlsx
@@ -587,7 +587,7 @@
         <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.219509300887439</v>
@@ -595,10 +595,18 @@
       <c r="I3" t="n">
         <v>-0.0357142857142857</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.228855721393035</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.323383084577114</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.573156742858294</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.5521332629992</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -622,6 +630,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.604258453613332</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.69278817728204</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.822857082802613</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.709436753971948</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.00256720071422389</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.725193946348951</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.56937332094604</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.00665664911533237</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.282250276066772</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.635115121376453</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.253623323927347</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.434469058332533</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.54582148127787</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.342646079168963</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.356780506130401</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.877498014305851</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.25839036329188</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.135707010973942</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.0650528551793745</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.40523610520823</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.0953915733832975</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.261090582690682</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.593343201691429</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.589214076824246</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.911071091148135</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.313882641735904</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.398979619301162</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.311970958432459</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.713319757818607</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.996727934248383</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.590854741645321</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.0324272476888656</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.74516342363694</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.703739218111441</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.375546811412481</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.374706000434567</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.364482802794702</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.369965865438812</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.527910729490808</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.861483786324356</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-1.41023892933372</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.374802654067743</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.155085217386124</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.870213674306349</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-1.11551119294015</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.441007692390191</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-4.65033061795466</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.233009502093509</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.23009381932063</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-2.32862519377958</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-1.16001494144506</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.298710657078186</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.0192106216344874</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.711211490300959</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.429419607442731</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.884751126480799</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-1.60568019735072</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.869312286067907</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.229103269621286</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.0802384442484878</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.65738980448839</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.613343958965337</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.579945653491821</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.0574953072039257</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-1.35120654188782</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.29077155986031</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.613199809149723</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.529333263328566</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.126657762161714</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.145549360766282</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.259871941360313</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.627334277632675</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.0537193426873404</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-1.88670417912621</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-1.02725204308107</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-0.610852457254879</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.53721129580575</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-1.12379937833819</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.66590826473403</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.156722301576901</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.241373715085034</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.90298283658845</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-1.05306410023079</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-1.15951388109934</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.1778763826657</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.263684710416493</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-0.343865485343076</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.630425963349811</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.0913876545912913</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.511194436447013</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.507060227180284</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.604419289888104</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-0.366598992072607</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-0.526246944972601</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-0.583707817686772</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-0.331413286543161</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.292334991571099</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-2.36849491413352</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-1.64148702915994</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-1.18040855300561</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-0.519330522052935</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-1.10735660192388</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.432246954994571</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-0.370596024730769</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-1.45433595434825</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-1.97503868276489</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.841035351913399</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.756000443794873</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.393320292767336</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-0.450456531282898</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.949378099625856</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.372491534858143</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.561451848494187</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.139520092275362</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-1.31975498360377</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.851343156582616</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.441894655643963</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-1.46247073201827</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-0.529821531681115</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.808967167871592</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.179602310500872</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.884574453897163</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.236652849079172</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.293559321640756</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.705609640607451</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.00954439168271282</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.14883747117634</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.348392396947323</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.487652666355939</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-0.558789306864596</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-0.712035386314655</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.832477942398582</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-1.25670641145743</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-1.05929040020832</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.615347014715813</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.0989509171511429</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.357133734849076</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.372778751614729</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.27539208392221</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.0361162346164539</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.832820279388135</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.130313386651301</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-0.543289126570999</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.681861114604966</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-0.197272667555539</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.726551540086398</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-0.200582507433554</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-1.09464960717846</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.227633819607918</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.38939250385816</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.278670656923017</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.23655809442741</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.243591804179243</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.198545314326069</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-0.408221807919721</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.375859195889556</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.427966675451503</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.190046272174069</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.221250753508417</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-0.389650573374907</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-1.05063819287505</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.155022529030108</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.321620082374839</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.852753238439322</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.66114340388737</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.106495378118773</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.743144058346572</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.537139165033076</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-1.10379725760126</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.397267658011278</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-0.0711631552540006</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.785496585777869</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-0.734023748574771</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.719235492470174</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-0.364636884592093</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.555629200250897</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-0.858496604943849</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.35825731997949</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.0144552163536955</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.170340999282789</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0.0974648707748462</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-0.188902053254986</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-0.935897471675381</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-0.0109904406792531</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-0.991796102340395</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.323050537932809</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-1.48206120115592</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.133214796591234</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.284382611571597</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-0.767135952983582</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.0934434337561543</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.364510350878335</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.702329082478503</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.800732820088365</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0.332493583149058</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-0.442382861364277</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-1.10509025863114</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-0.578164926939027</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.61970583609565</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.223488403778348</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
